--- a/docs/08_sprint_plan.xlsx
+++ b/docs/08_sprint_plan.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Story Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Backlog Status" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Forward" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dependencies" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Notes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog Status" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forward" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story Map'!$A$1:$F$45</definedName>
@@ -4243,7 +4243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8894,6 +8894,70 @@
       <c r="G138" t="inlineStr">
         <is>
           <t>ADR-0024 + DPIA §14 + docs/openapi/consent.yaml.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>US-121</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>17. Questionnaire Authoring</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Intake &amp; Registration</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>UBOS wave intake: store the accepted CSPro instrument as a FormVersion so the review compares against the registry, not an uploaded file. ADR-0034. See docs/stories/US-121-122_ubos_wave_intake.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>US-122</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>16. Data Integration Hub</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Data Integration Hub</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>UBOS wave intake: an unknown answer code is held as unmapped, never coerced. Needed before the first wave (late Oct/Nov 2026). ADR-0034/0032. See docs/stories/US-121-122_ubos_wave_intake.md.</t>
         </is>
       </c>
     </row>

--- a/docs/08_sprint_plan.xlsx
+++ b/docs/08_sprint_plan.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog Status" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forward" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Story Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Backlog Status" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Forward" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story Map'!$A$1:$F$45</definedName>
@@ -4243,7 +4243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8961,6 +8961,230 @@
         </is>
       </c>
     </row>
+    <row r="141" ht="112" customHeight="1">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>US-123</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-123-129_survey_data_hub.md. Foundation; blocks all production Hub promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="112" customHeight="1">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>US-124</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-123-129_survey_data_hub.md. Extends RawLanding; does not mutate historical payloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="112" customHeight="1">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>US-125</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-123-129_survey_data_hub.md. Builds on US-117..120 and ADR-0034.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="112" customHeight="1">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>US-126</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-123-129_survey_data_hub.md. Adds issue/review workflow above existing DQA results and DDUP candidates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="112" customHeight="1">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>US-127</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-123-129_survey_data_hub.md. Current JSX console is a design harness, not the production UI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="112" customHeight="1">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>US-128</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-123-129_survey_data_hub.md. Replaces direct in-process promotion with controlled exchange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="112" customHeight="1">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>US-129</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>20. Survey Data Hub Completion &amp; Separation</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>DIH (ING) / Survey Data Hub</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-123-129_survey_data_hub.md. Pilot-readiness gate; depends on US-123..128.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8973,7 +9197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9334,6 +9558,60 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Survey Data Hub foundation: separate DIH boundary, immutable Kobo archive, form/version lineage, and reviewer workflow.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DIH, INT, DAT-DQA, DAT-DDUP, API, SEC, Platform</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>US-123, US-124, US-125, US-126, US-127</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Survey Data Hub integration and pilot readiness: governed NSR exchange, reconciliation, monitoring, retention, and controlled Kobo pilot.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DIH, API, SEC, RPT, Platform</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>US-128, US-129</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9345,7 +9623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10185,6 +10463,70 @@
       <c r="F26" t="inlineStr">
         <is>
           <t>Statement v3 seeded with English real text + 6 placeholders flagged is_placeholder=True.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DEP-27</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kobo pilot DPA, project access, and approved encrypted raw/attachment archive location</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>S29 / S30</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MGLSD Legal + DPO + Kobo project owner + NITA-U</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Required before live Kobo credentials, attachment archive, or promotion are enabled. Archive-only technical testing may use synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DEP-28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NSR internal promotion API security and exchange-contract sign-off</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>S30 / pilot</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NSR MIS Architecture + Security + DPO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Must define service identity, network boundary, idempotency, sensitive-log policy, error contract, and reconciliation owner before production promotion.</t>
         </is>
       </c>
     </row>

--- a/docs/08_sprint_plan.xlsx
+++ b/docs/08_sprint_plan.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Status" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Story Map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Backlog Status" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Forward" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dependencies" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Notes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog Status" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forward" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Story Map'!$A$1:$F$45</definedName>
@@ -4243,7 +4243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9182,6 +9182,70 @@
       <c r="G147" t="inlineStr">
         <is>
           <t>Proposed 22 Sep 2026. See docs/stories/US-123-129_survey_data_hub.md. Pilot-readiness gate; depends on US-123..128.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>US-130</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>16. Data Integration Hub</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>DIH (ING) / SEC</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-130-131_rejected_record_lifecycle.md. Retention period is a DPO decision; do not default it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>US-131</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>16. Data Integration Hub</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>DIH (ING) / GRM</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Proposed 22 Sep 2026. See docs/stories/US-130-131_rejected_record_lifecycle.md. Depends on the ADR-0031/0033 SMS sender and on GRM accepting a grievance with no registry entry.</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10527,6 +10591,38 @@
       <c r="F28" t="inlineStr">
         <is>
           <t>Must define service identity, network boundary, idempotency, sensitive-log policy, error contract, and reconciliation owner before production promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DEP-29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Retention period for rejected/quarantined staging records, and transactional-notification policy for rejections</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US-130 / US-131</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Data Protection Officer + NSR Unit</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blocks both stories. The period and the bulk-vs-case notification policy are governance decisions, not defaults a developer should pick.</t>
         </is>
       </c>
     </row>

--- a/docs/08_sprint_plan.xlsx
+++ b/docs/08_sprint_plan.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1553,6 +1553,34 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Current delivery</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Direct household enrolment — Beneficiaries selection panel, canonical Programme + effective DSA + saved geography validation, atomic ProgrammeEnrolment batch, audit and cross-view SSOT checks.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1564,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4231,6 +4259,38 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Current/direct-household-enrolment</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>(working tree)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OI-S25-4, US-037, US-039</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>REF, partners, design</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Direct household enrolment is delivered from Beneficiaries against canonical ProgrammeEnrolment; no deferred endpoint or separate roster source.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4243,7 +4303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9246,6 +9306,43 @@
       <c r="G149" t="inlineStr">
         <is>
           <t>Proposed 22 Sep 2026. See docs/stories/US-130-131_rejected_record_lifecycle.md. Depends on the ADR-0031/0033 SMS sender and on GRM accepting a grievance with no registry entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>OI-S25-4</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Current/direct-household-enrolment</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>7. Programme Referral &amp; Enrolment</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Programme Referral &amp; Enrolment</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Direct household enrolment: server-backed multi-select, effective DSA/programme geography eligibility, atomic ProgrammeEnrolment writes, audit, and shared beneficiary/household/programme roster reads.</t>
         </is>
       </c>
     </row>

--- a/docs/08_sprint_plan.xlsx
+++ b/docs/08_sprint_plan.xlsx
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1574,7 +1574,6 @@
           <t>Current delivery</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Direct household enrolment — Beneficiaries selection panel, canonical Programme + effective DSA + saved geography validation, atomic ProgrammeEnrolment batch, audit and cross-view SSOT checks.</t>
@@ -4267,12 +4266,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>(working tree)</t>
+          <t>df576fe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -9317,7 +9316,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
